--- a/data/trans_orig/P68-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P68-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35016</t>
+          <t>34898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59789</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52473</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80612</t>
+          <t>81510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116782</t>
+          <t>118486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141555</t>
+          <t>141673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112495</t>
+          <t>112076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128240</t>
+          <t>127849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237076</t>
+          <t>236178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265215</t>
+          <t>263661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120739</t>
+          <t>119845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>162859</t>
+          <t>163752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>62872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97834</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196259</t>
+          <t>195025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>249658</t>
+          <t>248051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393431</t>
+          <t>392538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435551</t>
+          <t>436445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241042</t>
+          <t>244682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>274406</t>
+          <t>276004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>645508</t>
+          <t>647115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698907</t>
+          <t>700141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105262</t>
+          <t>108902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146058</t>
+          <t>146952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57179</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86261</t>
+          <t>85650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171774</t>
+          <t>170742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>220081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>414133</t>
+          <t>413239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454929</t>
+          <t>451289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218286</t>
+          <t>218897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247368</t>
+          <t>248905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643666</t>
+          <t>644656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692963</t>
+          <t>693995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92670</t>
+          <t>93338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>132079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27489</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48402</t>
+          <t>48376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126776</t>
+          <t>127422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170691</t>
+          <t>171956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300257</t>
+          <t>300118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>339527</t>
+          <t>338859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120617</t>
+          <t>120643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141530</t>
+          <t>140918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430525</t>
+          <t>429260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474440</t>
+          <t>473794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>34869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58515</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73161</t>
+          <t>73797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104633</t>
+          <t>106126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128669</t>
+          <t>128279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43158</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56175</t>
+          <t>56095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154271</t>
+          <t>153635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180743</t>
+          <t>179527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1462</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1635</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>432161</t>
+          <t>434510</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>506905</t>
+          <t>510003</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>195809</t>
+          <t>196389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249326</t>
+          <t>247541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>644460</t>
+          <t>646055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>737682</t>
+          <t>740870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1386530</t>
+          <t>1383432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1461274</t>
+          <t>1458925</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>772138</t>
+          <t>773923</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825655</t>
+          <t>825075</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2177217</t>
+          <t>2174029</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2270439</t>
+          <t>2268844</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17161</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64258</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76139</t>
+          <t>76358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70640</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82708</t>
+          <t>82659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139591</t>
+          <t>140625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156870</t>
+          <t>156434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70740</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104135</t>
+          <t>104742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52514</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83721</t>
+          <t>82708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131448</t>
+          <t>132156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177134</t>
+          <t>177279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>279537</t>
+          <t>278930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>312932</t>
+          <t>310959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193471</t>
+          <t>194484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224678</t>
+          <t>223782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>483730</t>
+          <t>483585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>529416</t>
+          <t>528708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83534</t>
+          <t>82441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117734</t>
+          <t>118101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58540</t>
+          <t>58835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>89495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148452</t>
+          <t>151317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195632</t>
+          <t>198047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308418</t>
+          <t>308051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342618</t>
+          <t>343711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196761</t>
+          <t>195281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>226236</t>
+          <t>225941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>515296</t>
+          <t>512881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>562476</t>
+          <t>559611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74283</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111163</t>
+          <t>108450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29967</t>
+          <t>29837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54326</t>
+          <t>55037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112937</t>
+          <t>112338</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155072</t>
+          <t>156150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>255476</t>
+          <t>258189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292356</t>
+          <t>293650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172092</t>
+          <t>171381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>196581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>437985</t>
+          <t>436907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>480120</t>
+          <t>480719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>34157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>55951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>55898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82848</t>
+          <t>83486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102668</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123944</t>
+          <t>123194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144193</t>
+          <t>143555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171545</t>
+          <t>171143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -5427,97 +5427,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>300778</t>
+          <t>300958</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>363978</t>
+          <t>365159</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190384</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>244971</t>
+          <t>242807</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>506992</t>
+          <t>506861</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>587553</t>
+          <t>591211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1054727</t>
+          <t>1053546</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1117927</t>
+          <t>1117747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>703745</t>
+          <t>705909</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>758332</t>
+          <t>757957</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1779868</t>
+          <t>1776210</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1860429</t>
+          <t>1860560</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26136</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39245</t>
+          <t>39484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51885</t>
+          <t>52101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67293</t>
+          <t>67583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73721</t>
+          <t>72403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85894</t>
+          <t>85096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>130392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>149825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66359</t>
+          <t>65969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97467</t>
+          <t>98350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>35162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59121</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109610</t>
+          <t>108840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147532</t>
+          <t>150404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244689</t>
+          <t>243806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>275797</t>
+          <t>276187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214595</t>
+          <t>214061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239058</t>
+          <t>238554</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>468341</t>
+          <t>465469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506263</t>
+          <t>507033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95653</t>
+          <t>94989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132630</t>
+          <t>133320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57768</t>
+          <t>57753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89049</t>
+          <t>87813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160867</t>
+          <t>159950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209290</t>
+          <t>210081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>324322</t>
+          <t>323632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>361299</t>
+          <t>361963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226483</t>
+          <t>227719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257764</t>
+          <t>257779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>563194</t>
+          <t>562403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>611617</t>
+          <t>612534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>74299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108531</t>
+          <t>109318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>44646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71139</t>
+          <t>71471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126011</t>
+          <t>124548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169706</t>
+          <t>170304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>255077</t>
+          <t>254290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290438</t>
+          <t>289309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170982</t>
+          <t>170650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199148</t>
+          <t>197475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>436023</t>
+          <t>435425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>479718</t>
+          <t>481181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,44%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>32450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55993</t>
+          <t>57109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41592</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>60808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91969</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107622</t>
+          <t>106506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130814</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>62503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81690</t>
+          <t>81700</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175285</t>
+          <t>175516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206624</t>
+          <t>206446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -8441,62 +8441,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1880</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5061</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5884</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8749,97 +8749,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -8862,97 +8862,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>318451</t>
+          <t>316701</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>384700</t>
+          <t>384864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>191645</t>
+          <t>189877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>525085</t>
+          <t>523190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>613144</t>
+          <t>606579</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1025637</t>
+          <t>1025473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1091886</t>
+          <t>1093636</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>786267</t>
+          <t>790028</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>840409</t>
+          <t>842177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1829247</t>
+          <t>1835812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1917306</t>
+          <t>1919201</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26908</t>
+          <t>26196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>68078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82560</t>
+          <t>82530</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52569</t>
+          <t>53281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>71726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127501</t>
+          <t>128849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151220</t>
+          <t>151555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42543</t>
+          <t>43493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78946</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68083</t>
+          <t>69910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>76216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135916</t>
+          <t>136132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264997</t>
+          <t>263922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>301400</t>
+          <t>300450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278039</t>
+          <t>276212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320182</t>
+          <t>320364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554149</t>
+          <t>553933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>616531</t>
+          <t>613849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78807</t>
+          <t>79707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112500</t>
+          <t>114597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63290</t>
+          <t>63065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>89155</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150946</t>
+          <t>149793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>193882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344405</t>
+          <t>342308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>378098</t>
+          <t>377198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258966</t>
+          <t>257985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283850</t>
+          <t>284075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610628</t>
+          <t>610163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653099</t>
+          <t>654252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41647</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169420</t>
+          <t>169961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>125381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228126</t>
+          <t>225947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138976</t>
+          <t>136236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351234</t>
+          <t>357358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>572205</t>
+          <t>571664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>699978</t>
+          <t>700838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>220634</t>
+          <t>222813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322698</t>
+          <t>323379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>839151</t>
+          <t>833027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1051409</t>
+          <t>1054149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53454</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80695</t>
+          <t>82290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>46698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65443</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107213</t>
+          <t>107691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139315</t>
+          <t>141644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>215145</t>
+          <t>213550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242386</t>
+          <t>241626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140643</t>
+          <t>139690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160091</t>
+          <t>159388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362611</t>
+          <t>360282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394713</t>
+          <t>394235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24702</t>
+          <t>24785</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>31641</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -11728,97 +11728,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -11841,97 +11841,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>221407</t>
+          <t>221500</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>403545</t>
+          <t>403377</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>301871</t>
+          <t>296499</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>435034</t>
+          <t>430214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>547345</t>
+          <t>547157</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>784691</t>
+          <t>791217</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1537383</t>
+          <t>1537551</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1719521</t>
+          <t>1719428</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1010302</t>
+          <t>1015122</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1143465</t>
+          <t>1148837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2601573</t>
+          <t>2595047</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2838919</t>
+          <t>2839107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P68-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>35634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>58917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54027</t>
+          <t>51527</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81510</t>
+          <t>81102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118486</t>
+          <t>117654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141673</t>
+          <t>140937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112076</t>
+          <t>112578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127849</t>
+          <t>128097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>236178</t>
+          <t>236586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263661</t>
+          <t>266161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119845</t>
+          <t>122059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>163752</t>
+          <t>163259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62872</t>
+          <t>63981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94194</t>
+          <t>94852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195025</t>
+          <t>197418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248051</t>
+          <t>249017</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392538</t>
+          <t>393031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436445</t>
+          <t>434231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>244682</t>
+          <t>244024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>276004</t>
+          <t>274895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647115</t>
+          <t>646149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>700141</t>
+          <t>697748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108902</t>
+          <t>106920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146952</t>
+          <t>147363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>55971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>86806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170742</t>
+          <t>173379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220081</t>
+          <t>222412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413239</t>
+          <t>412828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451289</t>
+          <t>453271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218897</t>
+          <t>217741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248905</t>
+          <t>248576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644656</t>
+          <t>642325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>693995</t>
+          <t>691358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93338</t>
+          <t>91628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132079</t>
+          <t>130230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28101</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48376</t>
+          <t>48659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127422</t>
+          <t>128161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171956</t>
+          <t>173188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300118</t>
+          <t>301967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338859</t>
+          <t>340569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>120360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140918</t>
+          <t>141983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429260</t>
+          <t>428028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>473794</t>
+          <t>473055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57022</t>
+          <t>57497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21703</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47905</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73797</t>
+          <t>73400</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106126</t>
+          <t>105651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128279</t>
+          <t>127987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42581</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56095</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153635</t>
+          <t>154032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179527</t>
+          <t>180053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>434510</t>
+          <t>430098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>510003</t>
+          <t>508849</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>190991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>247541</t>
+          <t>247029</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>646055</t>
+          <t>648329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>740870</t>
+          <t>738299</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1383432</t>
+          <t>1384586</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1458925</t>
+          <t>1463337</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>773923</t>
+          <t>774435</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825075</t>
+          <t>830473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2174029</t>
+          <t>2176600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2268844</t>
+          <t>2266570</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64230</t>
+          <t>63683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76358</t>
+          <t>76585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>70286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82659</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140625</t>
+          <t>139569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156434</t>
+          <t>156413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72713</t>
+          <t>71029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104742</t>
+          <t>104689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53410</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82708</t>
+          <t>82213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132156</t>
+          <t>132377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177279</t>
+          <t>177515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278930</t>
+          <t>278983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310959</t>
+          <t>312643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194484</t>
+          <t>194979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223782</t>
+          <t>224003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>483585</t>
+          <t>483349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>528708</t>
+          <t>528487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82441</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118101</t>
+          <t>117392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58835</t>
+          <t>59175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89495</t>
+          <t>88985</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151317</t>
+          <t>149919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198047</t>
+          <t>194221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308051</t>
+          <t>308760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343711</t>
+          <t>342996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195281</t>
+          <t>195791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>225941</t>
+          <t>225601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>512881</t>
+          <t>516707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559611</t>
+          <t>561009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72989</t>
+          <t>75363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108450</t>
+          <t>111809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29837</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55037</t>
+          <t>55670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112338</t>
+          <t>112565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156150</t>
+          <t>155146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258189</t>
+          <t>254830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293650</t>
+          <t>291276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171381</t>
+          <t>170748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196581</t>
+          <t>195866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>436907</t>
+          <t>437911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>480719</t>
+          <t>480492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55898</t>
+          <t>56670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83486</t>
+          <t>83565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123194</t>
+          <t>123719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36771</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53487</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143555</t>
+          <t>143476</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171143</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>300958</t>
+          <t>298880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>365159</t>
+          <t>363016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190709</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242807</t>
+          <t>245637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>506861</t>
+          <t>505548</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>591211</t>
+          <t>585496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1053546</t>
+          <t>1055689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1117747</t>
+          <t>1119825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>705909</t>
+          <t>703079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>757957</t>
+          <t>758007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1776210</t>
+          <t>1781925</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1860560</t>
+          <t>1861873</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39484</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52101</t>
+          <t>52538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67583</t>
+          <t>67484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72403</t>
+          <t>72579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85096</t>
+          <t>85731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130392</t>
+          <t>129500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149825</t>
+          <t>150222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65969</t>
+          <t>66472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98350</t>
+          <t>100529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35162</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59655</t>
+          <t>59504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108840</t>
+          <t>109348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150404</t>
+          <t>150898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243806</t>
+          <t>241627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>276187</t>
+          <t>275684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214061</t>
+          <t>214212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238554</t>
+          <t>238679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465469</t>
+          <t>464975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>507033</t>
+          <t>506525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94989</t>
+          <t>93165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133320</t>
+          <t>131005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57753</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87813</t>
+          <t>85674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159950</t>
+          <t>160908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210081</t>
+          <t>211961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>323632</t>
+          <t>325947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>361963</t>
+          <t>363787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227719</t>
+          <t>229858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257779</t>
+          <t>259043</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>562403</t>
+          <t>560523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>612534</t>
+          <t>611576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74299</t>
+          <t>74346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109318</t>
+          <t>108291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44646</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71471</t>
+          <t>70973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124548</t>
+          <t>126230</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170304</t>
+          <t>170247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254290</t>
+          <t>255317</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289309</t>
+          <t>289262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170650</t>
+          <t>171148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197475</t>
+          <t>199939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>435425</t>
+          <t>435482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>479499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57109</t>
+          <t>57943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21940</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41137</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60808</t>
+          <t>59792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91738</t>
+          <t>91470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106506</t>
+          <t>105672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>130365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62503</t>
+          <t>61935</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>82200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175516</t>
+          <t>175784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206446</t>
+          <t>207462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>316701</t>
+          <t>315797</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>384864</t>
+          <t>384409</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>189877</t>
+          <t>191223</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242145</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>523190</t>
+          <t>523285</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>606579</t>
+          <t>608126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1025473</t>
+          <t>1025928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1093636</t>
+          <t>1094540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>790028</t>
+          <t>789909</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>842177</t>
+          <t>840831</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1835812</t>
+          <t>1834265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1919201</t>
+          <t>1919106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26196</t>
+          <t>27807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78085</t>
+          <t>89573</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68078</t>
+          <t>75960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82530</t>
+          <t>95875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64133</t>
+          <t>74001</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53281</t>
+          <t>62093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71726</t>
+          <t>81853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>142217</t>
+          <t>163574</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128849</t>
+          <t>148159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151555</t>
+          <t>174767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84074</t>
+          <t>98791</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84074</t>
+          <t>98791</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84074</t>
+          <t>98791</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79477</t>
+          <t>89900</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79477</t>
+          <t>89900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79477</t>
+          <t>89900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>163550</t>
+          <t>188691</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163550</t>
+          <t>188691</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>163550</t>
+          <t>188691</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59074</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>49479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80021</t>
+          <t>91631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49949</t>
+          <t>51512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69910</t>
+          <t>65033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>109022</t>
+          <t>121105</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76216</t>
+          <t>97903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136132</t>
+          <t>147136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>284869</t>
+          <t>320098</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263922</t>
+          <t>298060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300450</t>
+          <t>340212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>296173</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276212</t>
+          <t>247363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320364</t>
+          <t>274453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>581043</t>
+          <t>580981</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>553933</t>
+          <t>554950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>613849</t>
+          <t>604183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>343943</t>
+          <t>389691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>343943</t>
+          <t>389691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>343943</t>
+          <t>389691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>346122</t>
+          <t>312396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>346122</t>
+          <t>312396</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>346122</t>
+          <t>312396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>690065</t>
+          <t>702086</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>690065</t>
+          <t>702086</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>690065</t>
+          <t>702086</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95531</t>
+          <t>109977</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79707</t>
+          <t>91276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114597</t>
+          <t>130605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75552</t>
+          <t>86641</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63065</t>
+          <t>72817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89155</t>
+          <t>101766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>171084</t>
+          <t>196618</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149793</t>
+          <t>172724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193882</t>
+          <t>221566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>361374</t>
+          <t>423298</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>342308</t>
+          <t>402670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>377198</t>
+          <t>441999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>271588</t>
+          <t>306175</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257985</t>
+          <t>291050</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284075</t>
+          <t>319999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>632961</t>
+          <t>729474</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610163</t>
+          <t>704526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654252</t>
+          <t>753368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>456905</t>
+          <t>533275</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>456905</t>
+          <t>533275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456905</t>
+          <t>533275</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347140</t>
+          <t>392816</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347140</t>
+          <t>392816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347140</t>
+          <t>392816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>804045</t>
+          <t>926092</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>804045</t>
+          <t>926092</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>804045</t>
+          <t>926092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>108553</t>
+          <t>120530</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>101254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169961</t>
+          <t>141606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>126515</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125381</t>
+          <t>113134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225947</t>
+          <t>141889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>263502</t>
+          <t>247045</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136236</t>
+          <t>222966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>357358</t>
+          <t>271635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>633072</t>
+          <t>419246</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>571664</t>
+          <t>398170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>700838</t>
+          <t>438522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>293811</t>
+          <t>322029</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222813</t>
+          <t>306655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323379</t>
+          <t>335410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>926883</t>
+          <t>741275</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>833027</t>
+          <t>716685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1054149</t>
+          <t>765354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>741625</t>
+          <t>539776</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>741625</t>
+          <t>539776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>741625</t>
+          <t>539776</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>448760</t>
+          <t>448544</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>448760</t>
+          <t>448544</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>448760</t>
+          <t>448544</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1190385</t>
+          <t>988320</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1190385</t>
+          <t>988320</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1190385</t>
+          <t>988320</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>67436</t>
+          <t>72023</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82290</t>
+          <t>86824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55507</t>
+          <t>61768</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46698</t>
+          <t>52180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>72198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>133791</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107691</t>
+          <t>116235</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141644</t>
+          <t>152820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>228404</t>
+          <t>252129</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213550</t>
+          <t>237328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241626</t>
+          <t>265422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>150579</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139690</t>
+          <t>158778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159388</t>
+          <t>178796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>378983</t>
+          <t>421337</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360282</t>
+          <t>402308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394235</t>
+          <t>438893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>295840</t>
+          <t>324152</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>295840</t>
+          <t>324152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>295840</t>
+          <t>324152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206086</t>
+          <t>230976</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206086</t>
+          <t>230976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206086</t>
+          <t>230976</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>501926</t>
+          <t>555128</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>501926</t>
+          <t>555128</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>501926</t>
+          <t>555128</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>32219</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24785</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>221500</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>403377</t>
+          <t>427477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>354215</t>
+          <t>345334</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296499</t>
+          <t>318644</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430214</t>
+          <t>374504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>693720</t>
+          <t>730344</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>547157</t>
+          <t>680340</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>791217</t>
+          <t>782010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1601423</t>
+          <t>1521659</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1537551</t>
+          <t>1479192</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1719428</t>
+          <t>1560676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1091121</t>
+          <t>1149017</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1015122</t>
+          <t>1119847</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1148837</t>
+          <t>1175707</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2692544</t>
+          <t>2670676</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2595047</t>
+          <t>2619010</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2839107</t>
+          <t>2720680</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P68-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
